--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979888</v>
+        <v>130979911</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590692</v>
+        <v>591152</v>
       </c>
       <c r="R2" t="n">
-        <v>6963278</v>
+        <v>6963132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979906</v>
+        <v>130979945</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591163</v>
+        <v>590594</v>
       </c>
       <c r="R3" t="n">
-        <v>6963104</v>
+        <v>6963385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979927</v>
+        <v>130979906</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590832</v>
+        <v>591163</v>
       </c>
       <c r="R4" t="n">
-        <v>6963235</v>
+        <v>6963104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979945</v>
+        <v>130979888</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590594</v>
+        <v>590692</v>
       </c>
       <c r="R5" t="n">
-        <v>6963385</v>
+        <v>6963278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,45 +1142,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979911</v>
+        <v>130979927</v>
       </c>
       <c r="B6" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591152</v>
+        <v>590832</v>
       </c>
       <c r="R6" t="n">
-        <v>6963132</v>
+        <v>6963235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979891</v>
+        <v>130979933</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590710</v>
+        <v>590658</v>
       </c>
       <c r="R7" t="n">
-        <v>6963217</v>
+        <v>6963312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979933</v>
+        <v>130979891</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590658</v>
+        <v>590710</v>
       </c>
       <c r="R8" t="n">
-        <v>6963312</v>
+        <v>6963217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2273,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979934</v>
+        <v>130979921</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2306,7 +2306,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590655</v>
+        <v>590951</v>
       </c>
       <c r="R16" t="n">
-        <v>6963332</v>
+        <v>6963242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979937</v>
+        <v>130979928</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590635</v>
+        <v>590813</v>
       </c>
       <c r="R17" t="n">
-        <v>6963366</v>
+        <v>6963212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979928</v>
+        <v>130979937</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590813</v>
+        <v>590635</v>
       </c>
       <c r="R18" t="n">
-        <v>6963212</v>
+        <v>6963366</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979921</v>
+        <v>130979934</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2666,7 +2666,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590951</v>
+        <v>590655</v>
       </c>
       <c r="R19" t="n">
-        <v>6963242</v>
+        <v>6963332</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,7 +2753,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979929</v>
+        <v>130979889</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590797</v>
+        <v>590701</v>
       </c>
       <c r="R20" t="n">
-        <v>6963219</v>
+        <v>6963240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979889</v>
+        <v>130979919</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590701</v>
+        <v>590971</v>
       </c>
       <c r="R21" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,7 +2993,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130979919</v>
+        <v>130979929</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590971</v>
+        <v>590797</v>
       </c>
       <c r="R22" t="n">
-        <v>6963236</v>
+        <v>6963219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979895</v>
+        <v>130979915</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3386,7 +3386,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590687</v>
+        <v>591100</v>
       </c>
       <c r="R25" t="n">
-        <v>6963193</v>
+        <v>6963185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,7 +3473,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979948</v>
+        <v>130979902</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590579</v>
+        <v>591003</v>
       </c>
       <c r="R26" t="n">
-        <v>6963330</v>
+        <v>6963091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979902</v>
+        <v>130979948</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591003</v>
+        <v>590579</v>
       </c>
       <c r="R27" t="n">
-        <v>6963091</v>
+        <v>6963330</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979915</v>
+        <v>130979895</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3746,7 +3746,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591100</v>
+        <v>590687</v>
       </c>
       <c r="R28" t="n">
-        <v>6963185</v>
+        <v>6963193</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979899</v>
+        <v>130979897</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,42 +4071,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590850</v>
+        <v>590726</v>
       </c>
       <c r="R31" t="n">
-        <v>6963133</v>
+        <v>6963153</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4138,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4148,12 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,7 +4167,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979914</v>
+        <v>130979946</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4223,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591126</v>
+        <v>590605</v>
       </c>
       <c r="R32" t="n">
-        <v>6963169</v>
+        <v>6963364</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4258,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4268,12 +4255,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4300,7 +4287,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979946</v>
+        <v>130979899</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4343,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590605</v>
+        <v>590850</v>
       </c>
       <c r="R33" t="n">
-        <v>6963364</v>
+        <v>6963133</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4378,7 +4365,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,7 +4375,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4420,10 +4407,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979897</v>
+        <v>130979914</v>
       </c>
       <c r="B34" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4431,34 +4418,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590726</v>
+        <v>591126</v>
       </c>
       <c r="R34" t="n">
-        <v>6963153</v>
+        <v>6963169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4500,7 +4495,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979912</v>
+        <v>130979923</v>
       </c>
       <c r="B36" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,34 +4658,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591115</v>
+        <v>590913</v>
       </c>
       <c r="R36" t="n">
-        <v>6963152</v>
+        <v>6963246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4717,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4727,7 +4735,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4874,7 +4887,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979923</v>
+        <v>130979901</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4917,10 +4930,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590913</v>
+        <v>590965</v>
       </c>
       <c r="R38" t="n">
-        <v>6963246</v>
+        <v>6963093</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4952,7 +4965,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4962,7 +4975,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4994,10 +5007,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979901</v>
+        <v>130979912</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,42 +5018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590965</v>
+        <v>591115</v>
       </c>
       <c r="R39" t="n">
-        <v>6963093</v>
+        <v>6963152</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5072,7 +5077,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5082,12 +5087,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,7 +5114,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130979890</v>
+        <v>130979925</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590704</v>
+        <v>590855</v>
       </c>
       <c r="R40" t="n">
-        <v>6963217</v>
+        <v>6963228</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5234,7 +5234,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B41" t="n">
         <v>57884</v>
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R41" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5354,7 +5354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979925</v>
+        <v>130979900</v>
       </c>
       <c r="B42" t="n">
         <v>57884</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590855</v>
+        <v>590843</v>
       </c>
       <c r="R42" t="n">
-        <v>6963228</v>
+        <v>6963130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130979936</v>
+        <v>130979917</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>91808</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5605,42 +5605,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>590647</v>
+        <v>591077</v>
       </c>
       <c r="R44" t="n">
-        <v>6963338</v>
+        <v>6963186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5672,7 +5664,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5682,12 +5674,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5701,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130979917</v>
+        <v>130979936</v>
       </c>
       <c r="B45" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5725,34 +5712,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591077</v>
+        <v>590647</v>
       </c>
       <c r="R45" t="n">
-        <v>6963186</v>
+        <v>6963338</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5794,7 +5789,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5941,7 +5941,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130979930</v>
+        <v>130979932</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5974,7 +5974,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590789</v>
+        <v>590660</v>
       </c>
       <c r="R47" t="n">
-        <v>6963216</v>
+        <v>6963313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130979932</v>
+        <v>130979930</v>
       </c>
       <c r="B50" t="n">
         <v>57884</v>
@@ -6334,7 +6334,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590660</v>
+        <v>590789</v>
       </c>
       <c r="R50" t="n">
-        <v>6963313</v>
+        <v>6963216</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6541,7 +6541,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979898</v>
+        <v>130979893</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590830</v>
+        <v>590717</v>
       </c>
       <c r="R52" t="n">
-        <v>6963134</v>
+        <v>6963211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6901,7 +6901,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979893</v>
+        <v>130979898</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590717</v>
+        <v>590830</v>
       </c>
       <c r="R55" t="n">
-        <v>6963211</v>
+        <v>6963134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -2753,7 +2753,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979889</v>
+        <v>130979919</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590701</v>
+        <v>590971</v>
       </c>
       <c r="R20" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979919</v>
+        <v>130979889</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590971</v>
+        <v>590701</v>
       </c>
       <c r="R21" t="n">
-        <v>6963236</v>
+        <v>6963240</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979897</v>
+        <v>130979946</v>
       </c>
       <c r="B31" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,34 +4071,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590726</v>
+        <v>590605</v>
       </c>
       <c r="R31" t="n">
-        <v>6963153</v>
+        <v>6963364</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4138,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4148,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,7 +4180,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979946</v>
+        <v>130979899</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4210,10 +4223,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590605</v>
+        <v>590850</v>
       </c>
       <c r="R32" t="n">
-        <v>6963364</v>
+        <v>6963133</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4245,7 +4258,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4255,7 +4268,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4287,7 +4300,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979899</v>
+        <v>130979914</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4330,10 +4343,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590850</v>
+        <v>591126</v>
       </c>
       <c r="R33" t="n">
-        <v>6963133</v>
+        <v>6963169</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4375,12 +4388,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4407,10 +4420,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979914</v>
+        <v>130979897</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,42 +4431,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591126</v>
+        <v>590726</v>
       </c>
       <c r="R34" t="n">
-        <v>6963169</v>
+        <v>6963153</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,7 +4490,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4495,12 +4500,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979923</v>
+        <v>130979912</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,42 +4658,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590913</v>
+        <v>591115</v>
       </c>
       <c r="R36" t="n">
-        <v>6963246</v>
+        <v>6963152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4725,7 +4717,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4735,12 +4727,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4767,7 +4754,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4810,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R37" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4845,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4855,7 +4842,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4887,7 +4874,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979901</v>
+        <v>130979944</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4930,10 +4917,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590965</v>
+        <v>590599</v>
       </c>
       <c r="R38" t="n">
-        <v>6963093</v>
+        <v>6963388</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4965,7 +4952,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4975,7 +4962,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5007,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979912</v>
+        <v>130979901</v>
       </c>
       <c r="B39" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,34 +5005,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591115</v>
+        <v>590965</v>
       </c>
       <c r="R39" t="n">
-        <v>6963152</v>
+        <v>6963093</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5077,7 +5072,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5087,7 +5082,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979893</v>
+        <v>130979905</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>91808</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,42 +6552,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590717</v>
+        <v>591056</v>
       </c>
       <c r="R52" t="n">
-        <v>6963211</v>
+        <v>6963042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6619,7 +6611,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6629,12 +6621,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6661,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979903</v>
+        <v>130979941</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,42 +6659,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591048</v>
+        <v>590615</v>
       </c>
       <c r="R53" t="n">
-        <v>6963038</v>
+        <v>6963396</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6739,7 +6718,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6749,12 +6728,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6781,7 +6755,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6824,10 +6798,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R54" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6859,7 +6833,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6869,7 +6843,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6901,7 +6875,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979898</v>
+        <v>130979903</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6944,10 +6918,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590830</v>
+        <v>591048</v>
       </c>
       <c r="R55" t="n">
-        <v>6963134</v>
+        <v>6963038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6979,7 +6953,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6989,7 +6963,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7021,10 +6995,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979905</v>
+        <v>130979943</v>
       </c>
       <c r="B56" t="n">
-        <v>91808</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7032,34 +7006,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>591056</v>
+        <v>590608</v>
       </c>
       <c r="R56" t="n">
-        <v>6963042</v>
+        <v>6963380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7091,7 +7073,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7101,7 +7083,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7128,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979941</v>
+        <v>130979898</v>
       </c>
       <c r="B57" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7139,34 +7126,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590615</v>
+        <v>590830</v>
       </c>
       <c r="R57" t="n">
-        <v>6963396</v>
+        <v>6963134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7198,7 +7193,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7208,7 +7203,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979911</v>
+        <v>130979945</v>
       </c>
       <c r="B2" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591152</v>
+        <v>590594</v>
       </c>
       <c r="R2" t="n">
-        <v>6963132</v>
+        <v>6963385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979945</v>
+        <v>130979906</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -825,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590594</v>
+        <v>591163</v>
       </c>
       <c r="R3" t="n">
-        <v>6963385</v>
+        <v>6963104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979906</v>
+        <v>130979888</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -945,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591163</v>
+        <v>590692</v>
       </c>
       <c r="R4" t="n">
-        <v>6963104</v>
+        <v>6963278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R5" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,53 +1155,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979927</v>
+        <v>130979911</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590832</v>
+        <v>591152</v>
       </c>
       <c r="R6" t="n">
-        <v>6963235</v>
+        <v>6963132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130979935</v>
+        <v>130979926</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,19 +1633,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1653,10 +1657,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590645</v>
+        <v>590852</v>
       </c>
       <c r="R10" t="n">
-        <v>6963341</v>
+        <v>6963248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979926</v>
+        <v>130979935</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>91829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,23 +1740,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590852</v>
+        <v>590645</v>
       </c>
       <c r="R11" t="n">
-        <v>6963248</v>
+        <v>6963341</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979924</v>
+        <v>130979909</v>
       </c>
       <c r="B13" t="n">
-        <v>80348</v>
+        <v>79244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590895</v>
+        <v>591185</v>
       </c>
       <c r="R13" t="n">
-        <v>6963262</v>
+        <v>6963058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979916</v>
+        <v>130979924</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>80349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591098</v>
+        <v>590895</v>
       </c>
       <c r="R14" t="n">
-        <v>6963187</v>
+        <v>6963262</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979909</v>
+        <v>130979916</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591185</v>
+        <v>591098</v>
       </c>
       <c r="R15" t="n">
-        <v>6963058</v>
+        <v>6963187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2753,7 +2753,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979919</v>
+        <v>130979889</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590971</v>
+        <v>590701</v>
       </c>
       <c r="R20" t="n">
-        <v>6963236</v>
+        <v>6963240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979889</v>
+        <v>130979919</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590701</v>
+        <v>590971</v>
       </c>
       <c r="R21" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3956,7 +3956,7 @@
         <v>130979947</v>
       </c>
       <c r="B30" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979946</v>
+        <v>130979897</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,42 +4071,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590605</v>
+        <v>590726</v>
       </c>
       <c r="R31" t="n">
-        <v>6963364</v>
+        <v>6963153</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4138,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4148,12 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,7 +4167,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979899</v>
+        <v>130979946</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4223,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590850</v>
+        <v>590605</v>
       </c>
       <c r="R32" t="n">
-        <v>6963133</v>
+        <v>6963364</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4258,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4268,7 +4255,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4300,7 +4287,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979914</v>
+        <v>130979899</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4343,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591126</v>
+        <v>590850</v>
       </c>
       <c r="R33" t="n">
-        <v>6963169</v>
+        <v>6963133</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4378,7 +4365,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4388,12 +4375,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4420,10 +4407,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979897</v>
+        <v>130979914</v>
       </c>
       <c r="B34" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4431,34 +4418,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590726</v>
+        <v>591126</v>
       </c>
       <c r="R34" t="n">
-        <v>6963153</v>
+        <v>6963169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4500,7 +4495,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979912</v>
+        <v>130979923</v>
       </c>
       <c r="B36" t="n">
-        <v>80348</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,34 +4658,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591115</v>
+        <v>590913</v>
       </c>
       <c r="R36" t="n">
-        <v>6963152</v>
+        <v>6963246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4717,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4727,7 +4735,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4754,7 +4767,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4797,10 +4810,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R37" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4832,7 +4845,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4842,7 +4855,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4874,7 +4887,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979944</v>
+        <v>130979901</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4917,10 +4930,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590599</v>
+        <v>590965</v>
       </c>
       <c r="R38" t="n">
-        <v>6963388</v>
+        <v>6963093</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4952,7 +4965,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4962,7 +4975,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4994,10 +5007,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979901</v>
+        <v>130979912</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,42 +5018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590965</v>
+        <v>591115</v>
       </c>
       <c r="R39" t="n">
-        <v>6963093</v>
+        <v>6963152</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5072,7 +5077,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5082,12 +5087,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5597,7 +5597,7 @@
         <v>130979917</v>
       </c>
       <c r="B44" t="n">
-        <v>91808</v>
+        <v>91809</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979905</v>
+        <v>130979941</v>
       </c>
       <c r="B52" t="n">
-        <v>91808</v>
+        <v>79244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,21 +6552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591056</v>
+        <v>590615</v>
       </c>
       <c r="R52" t="n">
-        <v>6963042</v>
+        <v>6963396</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6648,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979941</v>
+        <v>130979905</v>
       </c>
       <c r="B53" t="n">
-        <v>79243</v>
+        <v>91809</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590615</v>
+        <v>591056</v>
       </c>
       <c r="R53" t="n">
-        <v>6963396</v>
+        <v>6963042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979945</v>
+        <v>130979911</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590594</v>
+        <v>591152</v>
       </c>
       <c r="R2" t="n">
-        <v>6963385</v>
+        <v>6963132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979906</v>
+        <v>130979945</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591163</v>
+        <v>590594</v>
       </c>
       <c r="R3" t="n">
-        <v>6963104</v>
+        <v>6963385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979888</v>
+        <v>130979906</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590692</v>
+        <v>591163</v>
       </c>
       <c r="R4" t="n">
-        <v>6963278</v>
+        <v>6963104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R5" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,45 +1142,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979911</v>
+        <v>130979927</v>
       </c>
       <c r="B6" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591152</v>
+        <v>590832</v>
       </c>
       <c r="R6" t="n">
-        <v>6963132</v>
+        <v>6963235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979909</v>
+        <v>130979924</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591185</v>
+        <v>590895</v>
       </c>
       <c r="R13" t="n">
-        <v>6963058</v>
+        <v>6963262</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979924</v>
+        <v>130979916</v>
       </c>
       <c r="B14" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590895</v>
+        <v>591098</v>
       </c>
       <c r="R14" t="n">
-        <v>6963262</v>
+        <v>6963187</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979916</v>
+        <v>130979909</v>
       </c>
       <c r="B15" t="n">
         <v>79244</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591098</v>
+        <v>591185</v>
       </c>
       <c r="R15" t="n">
-        <v>6963187</v>
+        <v>6963058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979921</v>
+        <v>130979928</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590951</v>
+        <v>590813</v>
       </c>
       <c r="R16" t="n">
-        <v>6963242</v>
+        <v>6963212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2393,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979928</v>
+        <v>130979937</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590813</v>
+        <v>590635</v>
       </c>
       <c r="R17" t="n">
-        <v>6963212</v>
+        <v>6963366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979937</v>
+        <v>130979934</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2546,7 +2546,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590635</v>
+        <v>590655</v>
       </c>
       <c r="R18" t="n">
-        <v>6963366</v>
+        <v>6963332</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979934</v>
+        <v>130979921</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2666,7 +2666,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590655</v>
+        <v>590951</v>
       </c>
       <c r="R19" t="n">
-        <v>6963332</v>
+        <v>6963242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,34 +6552,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R52" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6611,7 +6619,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6621,7 +6629,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6648,10 +6661,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979905</v>
+        <v>130979903</v>
       </c>
       <c r="B53" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,34 +6672,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591056</v>
+        <v>591048</v>
       </c>
       <c r="R53" t="n">
-        <v>6963042</v>
+        <v>6963038</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6718,7 +6739,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6728,7 +6749,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6755,7 +6781,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979893</v>
+        <v>130979943</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6798,10 +6824,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590717</v>
+        <v>590608</v>
       </c>
       <c r="R54" t="n">
-        <v>6963211</v>
+        <v>6963380</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6833,7 +6859,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6843,7 +6869,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6875,7 +6901,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979903</v>
+        <v>130979898</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6918,10 +6944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>591048</v>
+        <v>590830</v>
       </c>
       <c r="R55" t="n">
-        <v>6963038</v>
+        <v>6963134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6953,7 +6979,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6963,7 +6989,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6995,10 +7021,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979943</v>
+        <v>130979941</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7006,42 +7032,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590608</v>
+        <v>590615</v>
       </c>
       <c r="R56" t="n">
-        <v>6963380</v>
+        <v>6963396</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7073,7 +7091,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7083,12 +7101,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7115,10 +7128,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979898</v>
+        <v>130979905</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7126,42 +7139,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590830</v>
+        <v>591056</v>
       </c>
       <c r="R57" t="n">
-        <v>6963134</v>
+        <v>6963042</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7193,7 +7198,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7203,12 +7208,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130979926</v>
+        <v>130979922</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,34 +1633,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590852</v>
+        <v>590936</v>
       </c>
       <c r="R10" t="n">
-        <v>6963248</v>
+        <v>6963244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1832,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130979922</v>
+        <v>130979926</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,42 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590936</v>
+        <v>590852</v>
       </c>
       <c r="R12" t="n">
-        <v>6963244</v>
+        <v>6963248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979924</v>
+        <v>130979916</v>
       </c>
       <c r="B13" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590895</v>
+        <v>591098</v>
       </c>
       <c r="R13" t="n">
-        <v>6963262</v>
+        <v>6963187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979916</v>
+        <v>130979909</v>
       </c>
       <c r="B14" t="n">
         <v>79244</v>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591098</v>
+        <v>591185</v>
       </c>
       <c r="R14" t="n">
-        <v>6963187</v>
+        <v>6963058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979909</v>
+        <v>130979924</v>
       </c>
       <c r="B15" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591185</v>
+        <v>590895</v>
       </c>
       <c r="R15" t="n">
-        <v>6963058</v>
+        <v>6963262</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979928</v>
+        <v>130979921</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590813</v>
+        <v>590951</v>
       </c>
       <c r="R16" t="n">
-        <v>6963212</v>
+        <v>6963242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2393,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979937</v>
+        <v>130979928</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590635</v>
+        <v>590813</v>
       </c>
       <c r="R17" t="n">
-        <v>6963366</v>
+        <v>6963212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979934</v>
+        <v>130979937</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2546,7 +2546,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590655</v>
+        <v>590635</v>
       </c>
       <c r="R18" t="n">
-        <v>6963332</v>
+        <v>6963366</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979921</v>
+        <v>130979934</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2666,7 +2666,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590951</v>
+        <v>590655</v>
       </c>
       <c r="R19" t="n">
-        <v>6963242</v>
+        <v>6963332</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3953,10 +3953,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B30" t="n">
-        <v>91809</v>
+        <v>80349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R30" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B31" t="n">
-        <v>80349</v>
+        <v>91809</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,21 +4071,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R31" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4647,7 +4647,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B36" t="n">
         <v>57884</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R36" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4767,7 +4767,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979944</v>
+        <v>130979901</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590599</v>
+        <v>590965</v>
       </c>
       <c r="R37" t="n">
-        <v>6963388</v>
+        <v>6963093</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979901</v>
+        <v>130979912</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4898,42 +4898,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590965</v>
+        <v>591115</v>
       </c>
       <c r="R38" t="n">
-        <v>6963093</v>
+        <v>6963152</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4965,7 +4957,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4975,12 +4967,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5007,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979912</v>
+        <v>130979923</v>
       </c>
       <c r="B39" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,34 +5005,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591115</v>
+        <v>590913</v>
       </c>
       <c r="R39" t="n">
-        <v>6963152</v>
+        <v>6963246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5077,7 +5072,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5087,7 +5082,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130979917</v>
+        <v>130979936</v>
       </c>
       <c r="B44" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5605,34 +5605,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591077</v>
+        <v>590647</v>
       </c>
       <c r="R44" t="n">
-        <v>6963186</v>
+        <v>6963338</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5664,7 +5672,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5674,7 +5682,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5701,10 +5714,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130979936</v>
+        <v>130979917</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,42 +5725,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590647</v>
+        <v>591077</v>
       </c>
       <c r="R45" t="n">
-        <v>6963338</v>
+        <v>6963186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5789,12 +5794,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,42 +6552,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R52" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6619,7 +6611,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6629,12 +6621,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6661,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979903</v>
+        <v>130979905</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,42 +6659,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591048</v>
+        <v>591056</v>
       </c>
       <c r="R53" t="n">
-        <v>6963038</v>
+        <v>6963042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6739,7 +6718,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6749,12 +6728,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6781,7 +6755,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6824,10 +6798,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R54" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6859,7 +6833,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6869,7 +6843,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6901,7 +6875,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979898</v>
+        <v>130979903</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6944,10 +6918,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590830</v>
+        <v>591048</v>
       </c>
       <c r="R55" t="n">
-        <v>6963134</v>
+        <v>6963038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6979,7 +6953,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6989,7 +6963,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7021,10 +6995,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979941</v>
+        <v>130979943</v>
       </c>
       <c r="B56" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7032,34 +7006,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590615</v>
+        <v>590608</v>
       </c>
       <c r="R56" t="n">
-        <v>6963396</v>
+        <v>6963380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7091,7 +7073,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7101,7 +7083,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7128,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979905</v>
+        <v>130979898</v>
       </c>
       <c r="B57" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7139,34 +7126,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>591056</v>
+        <v>590830</v>
       </c>
       <c r="R57" t="n">
-        <v>6963042</v>
+        <v>6963134</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7198,7 +7193,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7208,7 +7203,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979911</v>
+        <v>130979945</v>
       </c>
       <c r="B2" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591152</v>
+        <v>590594</v>
       </c>
       <c r="R2" t="n">
-        <v>6963132</v>
+        <v>6963385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979945</v>
+        <v>130979906</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -825,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590594</v>
+        <v>591163</v>
       </c>
       <c r="R3" t="n">
-        <v>6963385</v>
+        <v>6963104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979906</v>
+        <v>130979888</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -945,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591163</v>
+        <v>590692</v>
       </c>
       <c r="R4" t="n">
-        <v>6963104</v>
+        <v>6963278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R5" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,53 +1155,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979927</v>
+        <v>130979911</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590832</v>
+        <v>591152</v>
       </c>
       <c r="R6" t="n">
-        <v>6963235</v>
+        <v>6963132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979916</v>
+        <v>130979909</v>
       </c>
       <c r="B13" t="n">
         <v>79244</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591098</v>
+        <v>591185</v>
       </c>
       <c r="R13" t="n">
-        <v>6963187</v>
+        <v>6963058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979909</v>
+        <v>130979916</v>
       </c>
       <c r="B14" t="n">
         <v>79244</v>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591185</v>
+        <v>591098</v>
       </c>
       <c r="R14" t="n">
-        <v>6963058</v>
+        <v>6963187</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979915</v>
+        <v>130979904</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3386,7 +3386,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591100</v>
+        <v>591043</v>
       </c>
       <c r="R25" t="n">
-        <v>6963185</v>
+        <v>6963028</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,7 +3473,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979902</v>
+        <v>130979915</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3506,7 +3506,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591003</v>
+        <v>591100</v>
       </c>
       <c r="R26" t="n">
-        <v>6963091</v>
+        <v>6963185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979948</v>
+        <v>130979902</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590579</v>
+        <v>591003</v>
       </c>
       <c r="R27" t="n">
-        <v>6963330</v>
+        <v>6963091</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R28" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3833,7 +3833,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130979904</v>
+        <v>130979895</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591043</v>
+        <v>590687</v>
       </c>
       <c r="R29" t="n">
-        <v>6963028</v>
+        <v>6963193</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3953,10 +3953,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B30" t="n">
-        <v>80349</v>
+        <v>91809</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R30" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B31" t="n">
-        <v>91809</v>
+        <v>80349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,21 +4071,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R31" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979944</v>
+        <v>130979912</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,42 +4658,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590599</v>
+        <v>591115</v>
       </c>
       <c r="R36" t="n">
-        <v>6963388</v>
+        <v>6963152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4725,7 +4717,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4735,12 +4727,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4767,7 +4754,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979901</v>
+        <v>130979923</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4810,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590965</v>
+        <v>590913</v>
       </c>
       <c r="R37" t="n">
-        <v>6963093</v>
+        <v>6963246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4845,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4855,7 +4842,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4887,10 +4874,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979912</v>
+        <v>130979944</v>
       </c>
       <c r="B38" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4898,34 +4885,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591115</v>
+        <v>590599</v>
       </c>
       <c r="R38" t="n">
-        <v>6963152</v>
+        <v>6963388</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4957,7 +4952,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4967,7 +4962,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4994,7 +4994,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979923</v>
+        <v>130979901</v>
       </c>
       <c r="B39" t="n">
         <v>57884</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590913</v>
+        <v>590965</v>
       </c>
       <c r="R39" t="n">
-        <v>6963246</v>
+        <v>6963093</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979941</v>
+        <v>130979905</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,21 +6552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590615</v>
+        <v>591056</v>
       </c>
       <c r="R52" t="n">
-        <v>6963396</v>
+        <v>6963042</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6648,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979905</v>
+        <v>130979893</v>
       </c>
       <c r="B53" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,34 +6659,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591056</v>
+        <v>590717</v>
       </c>
       <c r="R53" t="n">
-        <v>6963042</v>
+        <v>6963211</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6718,7 +6726,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6728,7 +6736,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6755,7 +6768,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979893</v>
+        <v>130979903</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6798,10 +6811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590717</v>
+        <v>591048</v>
       </c>
       <c r="R54" t="n">
-        <v>6963211</v>
+        <v>6963038</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6833,7 +6846,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6843,7 +6856,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6875,7 +6888,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979903</v>
+        <v>130979943</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6918,10 +6931,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>591048</v>
+        <v>590608</v>
       </c>
       <c r="R55" t="n">
-        <v>6963038</v>
+        <v>6963380</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6953,7 +6966,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6963,7 +6976,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6995,7 +7008,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979943</v>
+        <v>130979898</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -7038,10 +7051,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590608</v>
+        <v>590830</v>
       </c>
       <c r="R56" t="n">
-        <v>6963380</v>
+        <v>6963134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7073,7 +7086,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7083,7 +7096,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7115,10 +7128,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979898</v>
+        <v>130979941</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7126,42 +7139,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590830</v>
+        <v>590615</v>
       </c>
       <c r="R57" t="n">
-        <v>6963134</v>
+        <v>6963396</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7193,7 +7198,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7203,12 +7208,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979945</v>
+        <v>130979911</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590594</v>
+        <v>591152</v>
       </c>
       <c r="R2" t="n">
-        <v>6963385</v>
+        <v>6963132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979906</v>
+        <v>130979888</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591163</v>
+        <v>590692</v>
       </c>
       <c r="R3" t="n">
-        <v>6963104</v>
+        <v>6963278</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979888</v>
+        <v>130979906</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590692</v>
+        <v>591163</v>
       </c>
       <c r="R4" t="n">
-        <v>6963278</v>
+        <v>6963104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1155,45 +1142,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979911</v>
+        <v>130979945</v>
       </c>
       <c r="B6" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591152</v>
+        <v>590594</v>
       </c>
       <c r="R6" t="n">
-        <v>6963132</v>
+        <v>6963385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979933</v>
+        <v>130979891</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590658</v>
+        <v>590710</v>
       </c>
       <c r="R7" t="n">
-        <v>6963312</v>
+        <v>6963217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979891</v>
+        <v>130979887</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590710</v>
+        <v>590601</v>
       </c>
       <c r="R8" t="n">
-        <v>6963217</v>
+        <v>6963311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,7 +1502,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979887</v>
+        <v>130979933</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590601</v>
+        <v>590658</v>
       </c>
       <c r="R9" t="n">
-        <v>6963311</v>
+        <v>6963312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130979922</v>
+        <v>130979926</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,42 +1633,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590936</v>
+        <v>590852</v>
       </c>
       <c r="R10" t="n">
-        <v>6963244</v>
+        <v>6963248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130979926</v>
+        <v>130979922</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,34 +1843,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590852</v>
+        <v>590936</v>
       </c>
       <c r="R12" t="n">
-        <v>6963248</v>
+        <v>6963244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1920,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979909</v>
+        <v>130979916</v>
       </c>
       <c r="B13" t="n">
         <v>79244</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591185</v>
+        <v>591098</v>
       </c>
       <c r="R13" t="n">
-        <v>6963058</v>
+        <v>6963187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979916</v>
+        <v>130979909</v>
       </c>
       <c r="B14" t="n">
         <v>79244</v>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591098</v>
+        <v>591185</v>
       </c>
       <c r="R14" t="n">
-        <v>6963187</v>
+        <v>6963058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2273,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979921</v>
+        <v>130979934</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2306,7 +2306,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590951</v>
+        <v>590655</v>
       </c>
       <c r="R16" t="n">
-        <v>6963242</v>
+        <v>6963332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979928</v>
+        <v>130979937</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590813</v>
+        <v>590635</v>
       </c>
       <c r="R17" t="n">
-        <v>6963212</v>
+        <v>6963366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979937</v>
+        <v>130979921</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590635</v>
+        <v>590951</v>
       </c>
       <c r="R18" t="n">
-        <v>6963366</v>
+        <v>6963242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979934</v>
+        <v>130979928</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2666,7 +2666,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590655</v>
+        <v>590813</v>
       </c>
       <c r="R19" t="n">
-        <v>6963332</v>
+        <v>6963212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,7 +2753,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979889</v>
+        <v>130979929</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590701</v>
+        <v>590797</v>
       </c>
       <c r="R20" t="n">
-        <v>6963240</v>
+        <v>6963219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979919</v>
+        <v>130979889</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590971</v>
+        <v>590701</v>
       </c>
       <c r="R21" t="n">
-        <v>6963236</v>
+        <v>6963240</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,7 +2993,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130979929</v>
+        <v>130979919</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590797</v>
+        <v>590971</v>
       </c>
       <c r="R22" t="n">
-        <v>6963219</v>
+        <v>6963236</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3113,7 +3113,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979908</v>
+        <v>130979918</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591153</v>
+        <v>591073</v>
       </c>
       <c r="R23" t="n">
-        <v>6963013</v>
+        <v>6963191</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3233,7 +3233,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979918</v>
+        <v>130979908</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591073</v>
+        <v>591153</v>
       </c>
       <c r="R24" t="n">
-        <v>6963191</v>
+        <v>6963013</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979904</v>
+        <v>130979895</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591043</v>
+        <v>590687</v>
       </c>
       <c r="R25" t="n">
-        <v>6963028</v>
+        <v>6963193</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3473,7 +3473,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979915</v>
+        <v>130979948</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3506,7 +3506,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591100</v>
+        <v>590579</v>
       </c>
       <c r="R26" t="n">
-        <v>6963185</v>
+        <v>6963330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979948</v>
+        <v>130979915</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3746,7 +3746,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590579</v>
+        <v>591100</v>
       </c>
       <c r="R28" t="n">
-        <v>6963330</v>
+        <v>6963185</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3833,7 +3833,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130979895</v>
+        <v>130979904</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590687</v>
+        <v>591043</v>
       </c>
       <c r="R29" t="n">
-        <v>6963193</v>
+        <v>6963028</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979946</v>
+        <v>130979899</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590605</v>
+        <v>590850</v>
       </c>
       <c r="R32" t="n">
-        <v>6963364</v>
+        <v>6963133</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4287,7 +4287,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979899</v>
+        <v>130979914</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590850</v>
+        <v>591126</v>
       </c>
       <c r="R33" t="n">
-        <v>6963133</v>
+        <v>6963169</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4407,7 +4407,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979914</v>
+        <v>130979946</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591126</v>
+        <v>590605</v>
       </c>
       <c r="R34" t="n">
-        <v>6963169</v>
+        <v>6963364</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4754,7 +4754,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R37" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4874,7 +4874,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R38" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5114,7 +5114,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130979925</v>
+        <v>130979890</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590855</v>
+        <v>590704</v>
       </c>
       <c r="R40" t="n">
-        <v>6963228</v>
+        <v>6963217</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5234,7 +5234,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130979890</v>
+        <v>130979900</v>
       </c>
       <c r="B41" t="n">
         <v>57884</v>
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590704</v>
+        <v>590843</v>
       </c>
       <c r="R41" t="n">
-        <v>6963217</v>
+        <v>6963130</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5354,7 +5354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979900</v>
+        <v>130979925</v>
       </c>
       <c r="B42" t="n">
         <v>57884</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590843</v>
+        <v>590855</v>
       </c>
       <c r="R42" t="n">
-        <v>6963130</v>
+        <v>6963228</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130979936</v>
+        <v>130979917</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5605,42 +5605,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>590647</v>
+        <v>591077</v>
       </c>
       <c r="R44" t="n">
-        <v>6963338</v>
+        <v>6963186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5672,7 +5664,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5682,12 +5674,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5701,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130979917</v>
+        <v>130979936</v>
       </c>
       <c r="B45" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5725,34 +5712,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591077</v>
+        <v>590647</v>
       </c>
       <c r="R45" t="n">
-        <v>6963186</v>
+        <v>6963338</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5794,7 +5789,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5941,7 +5941,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130979932</v>
+        <v>130979930</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5974,7 +5974,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590660</v>
+        <v>590789</v>
       </c>
       <c r="R47" t="n">
-        <v>6963313</v>
+        <v>6963216</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130979930</v>
+        <v>130979932</v>
       </c>
       <c r="B50" t="n">
         <v>57884</v>
@@ -6334,7 +6334,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590789</v>
+        <v>590660</v>
       </c>
       <c r="R50" t="n">
-        <v>6963216</v>
+        <v>6963313</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6648,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,42 +6659,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R53" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6726,7 +6718,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6736,12 +6728,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6768,7 +6755,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979903</v>
+        <v>130979893</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6811,10 +6798,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>591048</v>
+        <v>590717</v>
       </c>
       <c r="R54" t="n">
-        <v>6963038</v>
+        <v>6963211</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6846,7 +6833,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6856,7 +6843,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6888,7 +6875,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979943</v>
+        <v>130979898</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6931,10 +6918,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590608</v>
+        <v>590830</v>
       </c>
       <c r="R55" t="n">
-        <v>6963380</v>
+        <v>6963134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6966,7 +6953,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6976,7 +6963,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7008,7 +6995,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979898</v>
+        <v>130979903</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -7051,10 +7038,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590830</v>
+        <v>591048</v>
       </c>
       <c r="R56" t="n">
-        <v>6963134</v>
+        <v>6963038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7086,7 +7073,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7096,7 +7083,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7128,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979941</v>
+        <v>130979943</v>
       </c>
       <c r="B57" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7139,34 +7126,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590615</v>
+        <v>590608</v>
       </c>
       <c r="R57" t="n">
-        <v>6963396</v>
+        <v>6963380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7198,7 +7193,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7208,7 +7203,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130979911</v>
       </c>
       <c r="B2" t="n">
-        <v>80253</v>
+        <v>80254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979888</v>
+        <v>130979945</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590692</v>
+        <v>590594</v>
       </c>
       <c r="R3" t="n">
-        <v>6963278</v>
+        <v>6963385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R5" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979945</v>
+        <v>130979927</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590594</v>
+        <v>590832</v>
       </c>
       <c r="R6" t="n">
-        <v>6963385</v>
+        <v>6963235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1262,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979891</v>
+        <v>130979933</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590710</v>
+        <v>590658</v>
       </c>
       <c r="R7" t="n">
-        <v>6963217</v>
+        <v>6963312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979887</v>
+        <v>130979891</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590601</v>
+        <v>590710</v>
       </c>
       <c r="R8" t="n">
-        <v>6963311</v>
+        <v>6963217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,7 +1502,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979933</v>
+        <v>130979887</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590658</v>
+        <v>590601</v>
       </c>
       <c r="R9" t="n">
-        <v>6963312</v>
+        <v>6963311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1622,10 +1622,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130979926</v>
+        <v>130979935</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,23 +1633,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1657,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590852</v>
+        <v>590645</v>
       </c>
       <c r="R10" t="n">
-        <v>6963248</v>
+        <v>6963341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979935</v>
+        <v>130979926</v>
       </c>
       <c r="B11" t="n">
-        <v>91829</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,19 +1736,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590645</v>
+        <v>590852</v>
       </c>
       <c r="R11" t="n">
-        <v>6963341</v>
+        <v>6963248</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,7 +1955,7 @@
         <v>130979916</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979909</v>
+        <v>130979924</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>80350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591185</v>
+        <v>590895</v>
       </c>
       <c r="R14" t="n">
-        <v>6963058</v>
+        <v>6963262</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979924</v>
+        <v>130979909</v>
       </c>
       <c r="B15" t="n">
-        <v>80349</v>
+        <v>79245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590895</v>
+        <v>591185</v>
       </c>
       <c r="R15" t="n">
-        <v>6963262</v>
+        <v>6963058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979934</v>
+        <v>130979921</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2306,7 +2306,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590655</v>
+        <v>590951</v>
       </c>
       <c r="R16" t="n">
-        <v>6963332</v>
+        <v>6963242</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979937</v>
+        <v>130979928</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590635</v>
+        <v>590813</v>
       </c>
       <c r="R17" t="n">
-        <v>6963366</v>
+        <v>6963212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979921</v>
+        <v>130979937</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590951</v>
+        <v>590635</v>
       </c>
       <c r="R18" t="n">
-        <v>6963242</v>
+        <v>6963366</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979928</v>
+        <v>130979934</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2666,7 +2666,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590813</v>
+        <v>590655</v>
       </c>
       <c r="R19" t="n">
-        <v>6963212</v>
+        <v>6963332</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,7 +2753,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979929</v>
+        <v>130979889</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590797</v>
+        <v>590701</v>
       </c>
       <c r="R20" t="n">
-        <v>6963219</v>
+        <v>6963240</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2873,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979889</v>
+        <v>130979919</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590701</v>
+        <v>590971</v>
       </c>
       <c r="R21" t="n">
-        <v>6963240</v>
+        <v>6963236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,7 +2993,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130979919</v>
+        <v>130979929</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590971</v>
+        <v>590797</v>
       </c>
       <c r="R22" t="n">
-        <v>6963236</v>
+        <v>6963219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3113,7 +3113,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979918</v>
+        <v>130979908</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591073</v>
+        <v>591153</v>
       </c>
       <c r="R23" t="n">
-        <v>6963191</v>
+        <v>6963013</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3233,7 +3233,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979908</v>
+        <v>130979918</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591153</v>
+        <v>591073</v>
       </c>
       <c r="R24" t="n">
-        <v>6963013</v>
+        <v>6963191</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979895</v>
+        <v>130979915</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3386,7 +3386,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590687</v>
+        <v>591100</v>
       </c>
       <c r="R25" t="n">
-        <v>6963193</v>
+        <v>6963185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,7 +3473,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979948</v>
+        <v>130979902</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590579</v>
+        <v>591003</v>
       </c>
       <c r="R26" t="n">
-        <v>6963330</v>
+        <v>6963091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979902</v>
+        <v>130979948</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591003</v>
+        <v>590579</v>
       </c>
       <c r="R27" t="n">
-        <v>6963091</v>
+        <v>6963330</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979915</v>
+        <v>130979895</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3746,7 +3746,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591100</v>
+        <v>590687</v>
       </c>
       <c r="R28" t="n">
-        <v>6963185</v>
+        <v>6963193</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3953,10 +3953,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B30" t="n">
-        <v>91809</v>
+        <v>80350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R30" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B31" t="n">
-        <v>80349</v>
+        <v>91810</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,21 +4071,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R31" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979899</v>
+        <v>130979946</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590850</v>
+        <v>590605</v>
       </c>
       <c r="R32" t="n">
-        <v>6963133</v>
+        <v>6963364</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4287,7 +4287,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979914</v>
+        <v>130979899</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591126</v>
+        <v>590850</v>
       </c>
       <c r="R33" t="n">
-        <v>6963169</v>
+        <v>6963133</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4407,7 +4407,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979946</v>
+        <v>130979914</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590605</v>
+        <v>591126</v>
       </c>
       <c r="R34" t="n">
-        <v>6963364</v>
+        <v>6963169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979912</v>
+        <v>130979923</v>
       </c>
       <c r="B36" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,34 +4658,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591115</v>
+        <v>590913</v>
       </c>
       <c r="R36" t="n">
-        <v>6963152</v>
+        <v>6963246</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4717,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4727,7 +4735,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4874,7 +4887,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979923</v>
+        <v>130979901</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4917,10 +4930,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590913</v>
+        <v>590965</v>
       </c>
       <c r="R38" t="n">
-        <v>6963246</v>
+        <v>6963093</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4952,7 +4965,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4962,7 +4975,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4994,10 +5007,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979901</v>
+        <v>130979912</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5005,42 +5018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590965</v>
+        <v>591115</v>
       </c>
       <c r="R39" t="n">
-        <v>6963093</v>
+        <v>6963152</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5072,7 +5077,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5082,12 +5087,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,7 +5114,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130979890</v>
+        <v>130979925</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590704</v>
+        <v>590855</v>
       </c>
       <c r="R40" t="n">
-        <v>6963217</v>
+        <v>6963228</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5234,7 +5234,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B41" t="n">
         <v>57884</v>
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R41" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5354,7 +5354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979925</v>
+        <v>130979900</v>
       </c>
       <c r="B42" t="n">
         <v>57884</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590855</v>
+        <v>590843</v>
       </c>
       <c r="R42" t="n">
-        <v>6963228</v>
+        <v>6963130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5597,7 +5597,7 @@
         <v>130979917</v>
       </c>
       <c r="B44" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130979930</v>
+        <v>130979907</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5974,7 +5974,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590789</v>
+        <v>591205</v>
       </c>
       <c r="R47" t="n">
-        <v>6963216</v>
+        <v>6963087</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6061,7 +6061,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130979907</v>
+        <v>130979920</v>
       </c>
       <c r="B48" t="n">
         <v>57884</v>
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591205</v>
+        <v>590960</v>
       </c>
       <c r="R48" t="n">
-        <v>6963087</v>
+        <v>6963237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6181,7 +6181,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130979920</v>
+        <v>130979930</v>
       </c>
       <c r="B49" t="n">
         <v>57884</v>
@@ -6214,7 +6214,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590960</v>
+        <v>590789</v>
       </c>
       <c r="R49" t="n">
-        <v>6963237</v>
+        <v>6963216</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979905</v>
+        <v>130979941</v>
       </c>
       <c r="B52" t="n">
-        <v>91809</v>
+        <v>79245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,21 +6552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591056</v>
+        <v>590615</v>
       </c>
       <c r="R52" t="n">
-        <v>6963042</v>
+        <v>6963396</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6648,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979941</v>
+        <v>130979905</v>
       </c>
       <c r="B53" t="n">
-        <v>79244</v>
+        <v>91810</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6683,10 +6683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590615</v>
+        <v>591056</v>
       </c>
       <c r="R53" t="n">
-        <v>6963396</v>
+        <v>6963042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6755,7 +6755,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979893</v>
+        <v>130979903</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6798,10 +6798,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590717</v>
+        <v>591048</v>
       </c>
       <c r="R54" t="n">
-        <v>6963211</v>
+        <v>6963038</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6875,7 +6875,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979898</v>
+        <v>130979943</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590830</v>
+        <v>590608</v>
       </c>
       <c r="R55" t="n">
-        <v>6963134</v>
+        <v>6963380</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979903</v>
+        <v>130979898</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>591048</v>
+        <v>590830</v>
       </c>
       <c r="R56" t="n">
-        <v>6963038</v>
+        <v>6963134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7115,7 +7115,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979943</v>
+        <v>130979893</v>
       </c>
       <c r="B57" t="n">
         <v>57884</v>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590608</v>
+        <v>590717</v>
       </c>
       <c r="R57" t="n">
-        <v>6963380</v>
+        <v>6963211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979911</v>
+        <v>130979906</v>
       </c>
       <c r="B2" t="n">
-        <v>80254</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591152</v>
+        <v>591163</v>
       </c>
       <c r="R2" t="n">
-        <v>6963132</v>
+        <v>6963104</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979945</v>
+        <v>130979927</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -825,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590594</v>
+        <v>590832</v>
       </c>
       <c r="R3" t="n">
-        <v>6963385</v>
+        <v>6963235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,53 +915,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979906</v>
+        <v>130979911</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591163</v>
+        <v>591152</v>
       </c>
       <c r="R4" t="n">
-        <v>6963104</v>
+        <v>6963132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979888</v>
+        <v>130979945</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590692</v>
+        <v>590594</v>
       </c>
       <c r="R5" t="n">
-        <v>6963278</v>
+        <v>6963385</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R6" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979916</v>
+        <v>130979924</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>80350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591098</v>
+        <v>590895</v>
       </c>
       <c r="R13" t="n">
-        <v>6963187</v>
+        <v>6963262</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979924</v>
+        <v>130979909</v>
       </c>
       <c r="B14" t="n">
-        <v>80350</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590895</v>
+        <v>591185</v>
       </c>
       <c r="R14" t="n">
-        <v>6963262</v>
+        <v>6963058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979909</v>
+        <v>130979916</v>
       </c>
       <c r="B15" t="n">
         <v>79245</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591185</v>
+        <v>591098</v>
       </c>
       <c r="R15" t="n">
-        <v>6963058</v>
+        <v>6963187</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R27" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R28" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5941,7 +5941,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130979907</v>
+        <v>130979932</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>591205</v>
+        <v>590660</v>
       </c>
       <c r="R47" t="n">
-        <v>6963087</v>
+        <v>6963313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6061,7 +6061,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130979920</v>
+        <v>130979907</v>
       </c>
       <c r="B48" t="n">
         <v>57884</v>
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>590960</v>
+        <v>591205</v>
       </c>
       <c r="R48" t="n">
-        <v>6963237</v>
+        <v>6963087</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6181,7 +6181,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130979930</v>
+        <v>130979920</v>
       </c>
       <c r="B49" t="n">
         <v>57884</v>
@@ -6214,7 +6214,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590789</v>
+        <v>590960</v>
       </c>
       <c r="R49" t="n">
-        <v>6963216</v>
+        <v>6963237</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130979932</v>
+        <v>130979930</v>
       </c>
       <c r="B50" t="n">
         <v>57884</v>
@@ -6334,7 +6334,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590660</v>
+        <v>590789</v>
       </c>
       <c r="R50" t="n">
-        <v>6963313</v>
+        <v>6963216</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979906</v>
+        <v>130979911</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591163</v>
+        <v>591152</v>
       </c>
       <c r="R2" t="n">
-        <v>6963104</v>
+        <v>6963132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979927</v>
+        <v>130979945</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -838,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590832</v>
+        <v>590594</v>
       </c>
       <c r="R3" t="n">
-        <v>6963235</v>
+        <v>6963385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,45 +902,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979911</v>
+        <v>130979906</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591152</v>
+        <v>591163</v>
       </c>
       <c r="R4" t="n">
-        <v>6963132</v>
+        <v>6963104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979945</v>
+        <v>130979888</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590594</v>
+        <v>590692</v>
       </c>
       <c r="R5" t="n">
-        <v>6963385</v>
+        <v>6963278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R6" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -4647,10 +4647,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979923</v>
+        <v>130979912</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,42 +4658,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590913</v>
+        <v>591115</v>
       </c>
       <c r="R36" t="n">
-        <v>6963246</v>
+        <v>6963152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4725,7 +4717,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4735,12 +4727,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4767,7 +4754,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4810,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R37" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4845,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4855,7 +4842,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4887,7 +4874,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979901</v>
+        <v>130979944</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4930,10 +4917,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590965</v>
+        <v>590599</v>
       </c>
       <c r="R38" t="n">
-        <v>6963093</v>
+        <v>6963388</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4965,7 +4952,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4975,7 +4962,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5007,10 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979912</v>
+        <v>130979901</v>
       </c>
       <c r="B39" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5018,34 +5005,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591115</v>
+        <v>590965</v>
       </c>
       <c r="R39" t="n">
-        <v>6963152</v>
+        <v>6963093</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5077,7 +5072,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5087,7 +5082,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979911</v>
+        <v>130979945</v>
       </c>
       <c r="B2" t="n">
-        <v>80254</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591152</v>
+        <v>590594</v>
       </c>
       <c r="R2" t="n">
-        <v>6963132</v>
+        <v>6963385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979945</v>
+        <v>130979906</v>
       </c>
       <c r="B3" t="n">
         <v>57884</v>
@@ -825,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590594</v>
+        <v>591163</v>
       </c>
       <c r="R3" t="n">
-        <v>6963385</v>
+        <v>6963104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979906</v>
+        <v>130979888</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -945,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591163</v>
+        <v>590692</v>
       </c>
       <c r="R4" t="n">
-        <v>6963104</v>
+        <v>6963278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R5" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1123,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,53 +1155,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979927</v>
+        <v>130979911</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590832</v>
+        <v>591152</v>
       </c>
       <c r="R6" t="n">
-        <v>6963235</v>
+        <v>6963132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1625,7 +1625,7 @@
         <v>130979935</v>
       </c>
       <c r="B10" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979909</v>
+        <v>130979916</v>
       </c>
       <c r="B14" t="n">
         <v>79245</v>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591185</v>
+        <v>591098</v>
       </c>
       <c r="R14" t="n">
-        <v>6963058</v>
+        <v>6963187</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,7 +2166,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979916</v>
+        <v>130979909</v>
       </c>
       <c r="B15" t="n">
         <v>79245</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591098</v>
+        <v>591185</v>
       </c>
       <c r="R15" t="n">
-        <v>6963187</v>
+        <v>6963058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979895</v>
+        <v>130979948</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590687</v>
+        <v>590579</v>
       </c>
       <c r="R27" t="n">
-        <v>6963193</v>
+        <v>6963330</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979948</v>
+        <v>130979895</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590579</v>
+        <v>590687</v>
       </c>
       <c r="R28" t="n">
-        <v>6963330</v>
+        <v>6963193</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3953,10 +3953,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979897</v>
+        <v>130979947</v>
       </c>
       <c r="B30" t="n">
-        <v>80350</v>
+        <v>91813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590726</v>
+        <v>590591</v>
       </c>
       <c r="R30" t="n">
-        <v>6963153</v>
+        <v>6963354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979947</v>
+        <v>130979897</v>
       </c>
       <c r="B31" t="n">
-        <v>91810</v>
+        <v>80350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,21 +4071,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590591</v>
+        <v>590726</v>
       </c>
       <c r="R31" t="n">
-        <v>6963354</v>
+        <v>6963153</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5234,7 +5234,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130979890</v>
+        <v>130979900</v>
       </c>
       <c r="B41" t="n">
         <v>57884</v>
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590704</v>
+        <v>590843</v>
       </c>
       <c r="R41" t="n">
-        <v>6963217</v>
+        <v>6963130</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5354,7 +5354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B42" t="n">
         <v>57884</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R42" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130979917</v>
+        <v>130979936</v>
       </c>
       <c r="B44" t="n">
-        <v>91810</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5605,34 +5605,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591077</v>
+        <v>590647</v>
       </c>
       <c r="R44" t="n">
-        <v>6963186</v>
+        <v>6963338</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5664,7 +5672,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5674,7 +5682,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5701,10 +5714,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130979936</v>
+        <v>130979917</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>91813</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5712,42 +5725,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590647</v>
+        <v>591077</v>
       </c>
       <c r="R45" t="n">
-        <v>6963338</v>
+        <v>6963186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5779,7 +5784,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5789,12 +5794,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B52" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6552,34 +6552,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R52" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6611,7 +6619,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6621,7 +6629,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6648,10 +6661,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979905</v>
+        <v>130979903</v>
       </c>
       <c r="B53" t="n">
-        <v>91810</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,34 +6672,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591056</v>
+        <v>591048</v>
       </c>
       <c r="R53" t="n">
-        <v>6963042</v>
+        <v>6963038</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6718,7 +6739,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6728,7 +6749,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6755,7 +6781,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979903</v>
+        <v>130979943</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -6798,10 +6824,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>591048</v>
+        <v>590608</v>
       </c>
       <c r="R54" t="n">
-        <v>6963038</v>
+        <v>6963380</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6833,7 +6859,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6843,7 +6869,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6875,7 +6901,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979943</v>
+        <v>130979898</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6918,10 +6944,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590608</v>
+        <v>590830</v>
       </c>
       <c r="R55" t="n">
-        <v>6963380</v>
+        <v>6963134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6953,7 +6979,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6963,7 +6989,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6995,10 +7021,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979898</v>
+        <v>130979905</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>91813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7006,42 +7032,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590830</v>
+        <v>591056</v>
       </c>
       <c r="R56" t="n">
-        <v>6963134</v>
+        <v>6963042</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7073,7 +7091,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7083,12 +7101,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7115,10 +7128,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979893</v>
+        <v>130979941</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7126,42 +7139,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590717</v>
+        <v>590615</v>
       </c>
       <c r="R57" t="n">
-        <v>6963211</v>
+        <v>6963396</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7193,7 +7198,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7203,12 +7208,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979945</v>
+        <v>130979911</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590594</v>
+        <v>591152</v>
       </c>
       <c r="R2" t="n">
-        <v>6963385</v>
+        <v>6963132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -915,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979888</v>
+        <v>130979927</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -958,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590692</v>
+        <v>590832</v>
       </c>
       <c r="R4" t="n">
-        <v>6963278</v>
+        <v>6963235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979927</v>
+        <v>130979888</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590832</v>
+        <v>590692</v>
       </c>
       <c r="R5" t="n">
-        <v>6963235</v>
+        <v>6963278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,45 +1142,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979911</v>
+        <v>130979945</v>
       </c>
       <c r="B6" t="n">
-        <v>80254</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591152</v>
+        <v>590594</v>
       </c>
       <c r="R6" t="n">
-        <v>6963132</v>
+        <v>6963385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979933</v>
+        <v>130979891</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590658</v>
+        <v>590710</v>
       </c>
       <c r="R7" t="n">
-        <v>6963312</v>
+        <v>6963217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979891</v>
+        <v>130979887</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590710</v>
+        <v>590601</v>
       </c>
       <c r="R8" t="n">
-        <v>6963217</v>
+        <v>6963311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,7 +1502,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979887</v>
+        <v>130979933</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590601</v>
+        <v>590658</v>
       </c>
       <c r="R9" t="n">
-        <v>6963311</v>
+        <v>6963312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1625,7 +1625,7 @@
         <v>130979935</v>
       </c>
       <c r="B10" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>130979926</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979924</v>
+        <v>130979916</v>
       </c>
       <c r="B13" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590895</v>
+        <v>591098</v>
       </c>
       <c r="R13" t="n">
-        <v>6963262</v>
+        <v>6963187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979916</v>
+        <v>130979909</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591098</v>
+        <v>591185</v>
       </c>
       <c r="R14" t="n">
-        <v>6963187</v>
+        <v>6963058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979909</v>
+        <v>130979924</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591185</v>
+        <v>590895</v>
       </c>
       <c r="R15" t="n">
-        <v>6963058</v>
+        <v>6963262</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979937</v>
+        <v>130979934</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2546,7 +2546,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590635</v>
+        <v>590655</v>
       </c>
       <c r="R18" t="n">
-        <v>6963366</v>
+        <v>6963332</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979934</v>
+        <v>130979937</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2666,7 +2666,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590655</v>
+        <v>590635</v>
       </c>
       <c r="R19" t="n">
-        <v>6963332</v>
+        <v>6963366</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979915</v>
+        <v>130979895</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3386,7 +3386,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591100</v>
+        <v>590687</v>
       </c>
       <c r="R25" t="n">
-        <v>6963185</v>
+        <v>6963193</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,7 +3473,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979902</v>
+        <v>130979948</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591003</v>
+        <v>590579</v>
       </c>
       <c r="R26" t="n">
-        <v>6963091</v>
+        <v>6963330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3593,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979948</v>
+        <v>130979915</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3626,7 +3626,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590579</v>
+        <v>591100</v>
       </c>
       <c r="R27" t="n">
-        <v>6963330</v>
+        <v>6963185</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979895</v>
+        <v>130979902</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590687</v>
+        <v>591003</v>
       </c>
       <c r="R28" t="n">
-        <v>6963193</v>
+        <v>6963091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,7 +3956,7 @@
         <v>130979947</v>
       </c>
       <c r="B30" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979897</v>
+        <v>130979899</v>
       </c>
       <c r="B31" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,34 +4071,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590726</v>
+        <v>590850</v>
       </c>
       <c r="R31" t="n">
-        <v>6963153</v>
+        <v>6963133</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4138,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4148,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4287,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979899</v>
+        <v>130979897</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4298,42 +4311,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590850</v>
+        <v>590726</v>
       </c>
       <c r="R33" t="n">
-        <v>6963133</v>
+        <v>6963153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4370,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4375,12 +4380,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4650,7 +4650,7 @@
         <v>130979912</v>
       </c>
       <c r="B36" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979923</v>
+        <v>130979944</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590913</v>
+        <v>590599</v>
       </c>
       <c r="R37" t="n">
-        <v>6963246</v>
+        <v>6963388</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4874,7 +4874,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979944</v>
+        <v>130979923</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590599</v>
+        <v>590913</v>
       </c>
       <c r="R38" t="n">
-        <v>6963388</v>
+        <v>6963246</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5234,7 +5234,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130979900</v>
+        <v>130979890</v>
       </c>
       <c r="B41" t="n">
         <v>57884</v>
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590843</v>
+        <v>590704</v>
       </c>
       <c r="R41" t="n">
-        <v>6963130</v>
+        <v>6963217</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5354,7 +5354,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979890</v>
+        <v>130979900</v>
       </c>
       <c r="B42" t="n">
         <v>57884</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590704</v>
+        <v>590843</v>
       </c>
       <c r="R42" t="n">
-        <v>6963217</v>
+        <v>6963130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130979936</v>
+        <v>130979917</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5605,42 +5605,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>590647</v>
+        <v>591077</v>
       </c>
       <c r="R44" t="n">
-        <v>6963338</v>
+        <v>6963186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5672,7 +5664,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5682,12 +5674,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5701,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130979917</v>
+        <v>130979936</v>
       </c>
       <c r="B45" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5725,34 +5712,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591077</v>
+        <v>590647</v>
       </c>
       <c r="R45" t="n">
-        <v>6963186</v>
+        <v>6963338</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5784,7 +5779,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5794,7 +5789,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6541,7 +6541,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979893</v>
+        <v>130979903</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590717</v>
+        <v>591048</v>
       </c>
       <c r="R52" t="n">
-        <v>6963211</v>
+        <v>6963038</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6661,10 +6661,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979903</v>
+        <v>130979905</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,42 +6672,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591048</v>
+        <v>591056</v>
       </c>
       <c r="R53" t="n">
-        <v>6963038</v>
+        <v>6963042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6739,7 +6731,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6749,12 +6741,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6781,10 +6768,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979943</v>
+        <v>130979941</v>
       </c>
       <c r="B54" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6792,42 +6779,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590608</v>
+        <v>590615</v>
       </c>
       <c r="R54" t="n">
-        <v>6963380</v>
+        <v>6963396</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6859,7 +6838,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6869,12 +6848,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7021,10 +6995,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979905</v>
+        <v>130979943</v>
       </c>
       <c r="B56" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7032,34 +7006,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>591056</v>
+        <v>590608</v>
       </c>
       <c r="R56" t="n">
-        <v>6963042</v>
+        <v>6963380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7091,7 +7073,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7101,7 +7083,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7128,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979941</v>
+        <v>130979893</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7139,34 +7126,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590615</v>
+        <v>590717</v>
       </c>
       <c r="R57" t="n">
-        <v>6963396</v>
+        <v>6963211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7198,7 +7193,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7208,7 +7203,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130979911</v>
+        <v>130979905</v>
       </c>
       <c r="B2" t="n">
-        <v>80255</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591152</v>
+        <v>591056</v>
       </c>
       <c r="R2" t="n">
-        <v>6963132</v>
+        <v>6963042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130979906</v>
+        <v>130979917</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591163</v>
+        <v>591077</v>
       </c>
       <c r="R3" t="n">
-        <v>6963104</v>
+        <v>6963186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130979927</v>
+        <v>130979947</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,42 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590832</v>
+        <v>590591</v>
       </c>
       <c r="R4" t="n">
-        <v>6963235</v>
+        <v>6963354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,53 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130979888</v>
+        <v>130979909</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590692</v>
+        <v>591185</v>
       </c>
       <c r="R5" t="n">
-        <v>6963278</v>
+        <v>6963058</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,53 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130979945</v>
+        <v>130979916</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590594</v>
+        <v>591098</v>
       </c>
       <c r="R6" t="n">
-        <v>6963385</v>
+        <v>6963187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,53 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130979891</v>
+        <v>130979926</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590710</v>
+        <v>590852</v>
       </c>
       <c r="R7" t="n">
-        <v>6963217</v>
+        <v>6963248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,53 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130979887</v>
+        <v>130979941</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590601</v>
+        <v>590615</v>
       </c>
       <c r="R8" t="n">
-        <v>6963311</v>
+        <v>6963396</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,53 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130979933</v>
+        <v>130979911</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590658</v>
+        <v>591152</v>
       </c>
       <c r="R9" t="n">
-        <v>6963312</v>
+        <v>6963132</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130979935</v>
+        <v>130979897</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,19 +1542,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1653,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590645</v>
+        <v>590726</v>
       </c>
       <c r="R10" t="n">
-        <v>6963341</v>
+        <v>6963153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130979926</v>
+        <v>130979912</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590852</v>
+        <v>591115</v>
       </c>
       <c r="R11" t="n">
-        <v>6963248</v>
+        <v>6963152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130979922</v>
+        <v>130979924</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,42 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590936</v>
+        <v>590895</v>
       </c>
       <c r="R12" t="n">
-        <v>6963244</v>
+        <v>6963262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130979916</v>
+        <v>130979887</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,34 +1863,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591098</v>
+        <v>590601</v>
       </c>
       <c r="R13" t="n">
-        <v>6963187</v>
+        <v>6963311</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +1940,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130979909</v>
+        <v>130979888</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,34 +1983,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591185</v>
+        <v>590692</v>
       </c>
       <c r="R14" t="n">
-        <v>6963058</v>
+        <v>6963278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2050,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2060,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130979924</v>
+        <v>130979889</v>
       </c>
       <c r="B15" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,34 +2103,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590895</v>
+        <v>590701</v>
       </c>
       <c r="R15" t="n">
-        <v>6963262</v>
+        <v>6963240</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130979921</v>
+        <v>130979890</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590951</v>
+        <v>590704</v>
       </c>
       <c r="R16" t="n">
-        <v>6963242</v>
+        <v>6963217</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2290,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2300,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2393,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130979928</v>
+        <v>130979891</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590813</v>
+        <v>590710</v>
       </c>
       <c r="R17" t="n">
-        <v>6963212</v>
+        <v>6963217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2420,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2513,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130979934</v>
+        <v>130979893</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2546,7 +2485,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2556,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590655</v>
+        <v>590717</v>
       </c>
       <c r="R18" t="n">
-        <v>6963332</v>
+        <v>6963211</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2540,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130979937</v>
+        <v>130979894</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590635</v>
+        <v>590712</v>
       </c>
       <c r="R19" t="n">
-        <v>6963366</v>
+        <v>6963209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2650,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,12 +2660,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130979889</v>
+        <v>130979895</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590701</v>
+        <v>590687</v>
       </c>
       <c r="R20" t="n">
-        <v>6963240</v>
+        <v>6963193</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2780,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130979919</v>
+        <v>130979898</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590971</v>
+        <v>590830</v>
       </c>
       <c r="R21" t="n">
-        <v>6963236</v>
+        <v>6963134</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,7 +2890,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2961,7 +2900,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2993,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130979929</v>
+        <v>130979899</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590797</v>
+        <v>590850</v>
       </c>
       <c r="R22" t="n">
-        <v>6963219</v>
+        <v>6963133</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3113,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130979908</v>
+        <v>130979900</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3085,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3156,10 +3095,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591153</v>
+        <v>590843</v>
       </c>
       <c r="R23" t="n">
-        <v>6963013</v>
+        <v>6963130</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,12 +3140,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130979918</v>
+        <v>130979901</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3205,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3276,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591073</v>
+        <v>590965</v>
       </c>
       <c r="R24" t="n">
-        <v>6963191</v>
+        <v>6963093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3311,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,12 +3260,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,10 +3292,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130979895</v>
+        <v>130979902</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3396,10 +3335,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590687</v>
+        <v>591003</v>
       </c>
       <c r="R25" t="n">
-        <v>6963193</v>
+        <v>6963091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,12 +3380,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3473,10 +3412,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130979948</v>
+        <v>130979903</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3516,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590579</v>
+        <v>591048</v>
       </c>
       <c r="R26" t="n">
-        <v>6963330</v>
+        <v>6963038</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3551,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3561,12 +3500,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130979915</v>
+        <v>130979904</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3626,7 +3565,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3636,10 +3575,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591100</v>
+        <v>591043</v>
       </c>
       <c r="R27" t="n">
-        <v>6963185</v>
+        <v>6963028</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,7 +3610,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3681,12 +3620,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,10 +3652,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130979902</v>
+        <v>130979906</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3756,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591003</v>
+        <v>591163</v>
       </c>
       <c r="R28" t="n">
-        <v>6963091</v>
+        <v>6963104</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3791,7 +3730,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3740,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3833,10 +3772,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130979904</v>
+        <v>130979907</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,10 +3815,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591043</v>
+        <v>591205</v>
       </c>
       <c r="R29" t="n">
-        <v>6963028</v>
+        <v>6963087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3911,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3921,7 +3860,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3953,10 +3892,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130979947</v>
+        <v>130979908</v>
       </c>
       <c r="B30" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,34 +3903,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590591</v>
+        <v>591153</v>
       </c>
       <c r="R30" t="n">
-        <v>6963354</v>
+        <v>6963013</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4023,7 +3970,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4033,7 +3980,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4060,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130979899</v>
+        <v>130979913</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4093,7 +4045,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4103,10 +4055,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590850</v>
+        <v>591112</v>
       </c>
       <c r="R31" t="n">
-        <v>6963133</v>
+        <v>6963159</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4138,7 +4090,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4148,19 +4100,19 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>möjligt bohål i asp 3.5 meter upp</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -4180,10 +4132,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130979946</v>
+        <v>130979914</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4223,10 +4175,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590605</v>
+        <v>591126</v>
       </c>
       <c r="R32" t="n">
-        <v>6963364</v>
+        <v>6963169</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4258,7 +4210,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4268,12 +4220,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4300,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130979897</v>
+        <v>130979915</v>
       </c>
       <c r="B33" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4311,34 +4263,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590726</v>
+        <v>591100</v>
       </c>
       <c r="R33" t="n">
-        <v>6963153</v>
+        <v>6963185</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4370,7 +4330,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4380,7 +4340,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4407,10 +4372,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130979914</v>
+        <v>130979918</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4440,7 +4405,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4450,10 +4415,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591126</v>
+        <v>591073</v>
       </c>
       <c r="R34" t="n">
-        <v>6963169</v>
+        <v>6963191</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,7 +4450,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4495,12 +4460,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4527,10 +4492,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130979931</v>
+        <v>130979919</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4570,10 +4535,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590690</v>
+        <v>590971</v>
       </c>
       <c r="R35" t="n">
-        <v>6963301</v>
+        <v>6963236</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4605,7 +4570,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4580,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4647,10 +4612,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130979912</v>
+        <v>130979920</v>
       </c>
       <c r="B36" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,34 +4623,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591115</v>
+        <v>590960</v>
       </c>
       <c r="R36" t="n">
-        <v>6963152</v>
+        <v>6963237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4717,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4727,7 +4700,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4754,10 +4732,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130979944</v>
+        <v>130979921</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4797,10 +4775,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590599</v>
+        <v>590951</v>
       </c>
       <c r="R37" t="n">
-        <v>6963388</v>
+        <v>6963242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4832,7 +4810,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4842,7 +4820,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4874,10 +4852,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130979923</v>
+        <v>130979922</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4917,10 +4895,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590913</v>
+        <v>590936</v>
       </c>
       <c r="R38" t="n">
-        <v>6963246</v>
+        <v>6963244</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4952,7 +4930,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4962,7 +4940,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4994,10 +4972,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130979901</v>
+        <v>130979923</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5037,10 +5015,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590965</v>
+        <v>590913</v>
       </c>
       <c r="R39" t="n">
-        <v>6963093</v>
+        <v>6963246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5072,7 +5050,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5082,7 +5060,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5117,7 +5095,7 @@
         <v>130979925</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5234,10 +5212,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130979890</v>
+        <v>130979927</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5277,10 +5255,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590704</v>
+        <v>590832</v>
       </c>
       <c r="R41" t="n">
-        <v>6963217</v>
+        <v>6963235</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5290,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5300,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5354,10 +5332,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130979900</v>
+        <v>130979928</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5397,10 +5375,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590843</v>
+        <v>590813</v>
       </c>
       <c r="R42" t="n">
-        <v>6963130</v>
+        <v>6963212</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5432,7 +5410,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5442,7 +5420,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5474,10 +5452,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130979894</v>
+        <v>130979929</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5517,10 +5495,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>590712</v>
+        <v>590797</v>
       </c>
       <c r="R43" t="n">
-        <v>6963209</v>
+        <v>6963219</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5552,7 +5530,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5562,7 +5540,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5594,10 +5572,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130979917</v>
+        <v>130979930</v>
       </c>
       <c r="B44" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5605,34 +5583,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591077</v>
+        <v>590789</v>
       </c>
       <c r="R44" t="n">
-        <v>6963186</v>
+        <v>6963216</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5664,7 +5650,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5674,7 +5660,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5701,10 +5692,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130979936</v>
+        <v>130979931</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5734,7 +5725,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5744,10 +5735,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590647</v>
+        <v>590690</v>
       </c>
       <c r="R45" t="n">
-        <v>6963338</v>
+        <v>6963301</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5779,7 +5770,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5789,12 +5780,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5821,10 +5812,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130979940</v>
+        <v>130979932</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5864,10 +5855,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>590594</v>
+        <v>590660</v>
       </c>
       <c r="R46" t="n">
-        <v>6963404</v>
+        <v>6963313</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5899,7 +5890,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5909,7 +5900,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5941,10 +5932,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130979932</v>
+        <v>130979933</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5984,10 +5975,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590660</v>
+        <v>590658</v>
       </c>
       <c r="R47" t="n">
-        <v>6963313</v>
+        <v>6963312</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6019,7 +6010,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6029,7 +6020,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6061,10 +6052,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130979907</v>
+        <v>130979934</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6094,7 +6085,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6104,10 +6095,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591205</v>
+        <v>590655</v>
       </c>
       <c r="R48" t="n">
-        <v>6963087</v>
+        <v>6963332</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6139,7 +6130,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6149,12 +6140,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6181,10 +6172,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130979920</v>
+        <v>130979936</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6214,7 +6205,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6224,10 +6215,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590960</v>
+        <v>590647</v>
       </c>
       <c r="R49" t="n">
-        <v>6963237</v>
+        <v>6963338</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6259,7 +6250,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6269,12 +6260,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>Äldre sannolikt bohål i grantickerötad gran. Omkring 1.5 meter ovan mark. Bohålsdiametern är ungefär 4.5 cm. I lämplig biotop för arten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6301,10 +6292,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130979930</v>
+        <v>130979937</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6334,7 +6325,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6344,10 +6335,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590789</v>
+        <v>590635</v>
       </c>
       <c r="R50" t="n">
-        <v>6963216</v>
+        <v>6963366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6379,7 +6370,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6389,12 +6380,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6421,10 +6412,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130979913</v>
+        <v>130979939</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6454,7 +6445,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6464,10 +6455,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591112</v>
+        <v>590592</v>
       </c>
       <c r="R51" t="n">
-        <v>6963159</v>
+        <v>6963412</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6499,7 +6490,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6509,19 +6500,19 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>möjligt bohål i asp 3.5 meter upp</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="b">
         <v>0</v>
@@ -6541,10 +6532,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130979903</v>
+        <v>130979940</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6584,10 +6575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591048</v>
+        <v>590594</v>
       </c>
       <c r="R52" t="n">
-        <v>6963038</v>
+        <v>6963404</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6619,7 +6610,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6629,12 +6620,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6661,10 +6652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130979905</v>
+        <v>130979943</v>
       </c>
       <c r="B53" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6672,34 +6663,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591056</v>
+        <v>590608</v>
       </c>
       <c r="R53" t="n">
-        <v>6963042</v>
+        <v>6963380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6731,7 +6730,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6741,7 +6740,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6768,10 +6772,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130979941</v>
+        <v>130979944</v>
       </c>
       <c r="B54" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6779,34 +6783,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Långnäset, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590615</v>
+        <v>590599</v>
       </c>
       <c r="R54" t="n">
-        <v>6963396</v>
+        <v>6963388</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6838,7 +6850,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6848,7 +6860,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6875,10 +6892,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130979898</v>
+        <v>130979945</v>
       </c>
       <c r="B55" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6918,10 +6935,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590830</v>
+        <v>590594</v>
       </c>
       <c r="R55" t="n">
-        <v>6963134</v>
+        <v>6963385</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6953,7 +6970,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6963,7 +6980,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6995,10 +7012,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130979943</v>
+        <v>130979946</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7038,10 +7055,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590608</v>
+        <v>590605</v>
       </c>
       <c r="R56" t="n">
-        <v>6963380</v>
+        <v>6963364</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7073,7 +7090,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7083,7 +7100,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7115,10 +7132,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130979893</v>
+        <v>130979948</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7158,10 +7175,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590717</v>
+        <v>590579</v>
       </c>
       <c r="R57" t="n">
-        <v>6963211</v>
+        <v>6963330</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7193,7 +7210,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7203,12 +7220,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 3579-2026 artfynd.xlsx
+++ b/artfynd/A 3579-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979917</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979909</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979916</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979941</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979911</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979897</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979912</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979924</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979887</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979889</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2329,6 +2404,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979890</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2449,6 +2529,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979891</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2569,6 +2654,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979893</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2689,6 +2779,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979894</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2809,6 +2904,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979895</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2929,6 +3029,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979898</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3049,6 +3154,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979899</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3169,6 +3279,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3289,6 +3404,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979901</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3409,6 +3529,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979902</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3529,6 +3654,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979903</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3649,6 +3779,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979904</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3769,6 +3904,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979906</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3889,6 +4029,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979907</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4009,6 +4154,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979908</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4129,6 +4279,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979913</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4249,6 +4404,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979914</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4369,6 +4529,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979915</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4489,6 +4654,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979918</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4609,6 +4779,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979919</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4729,6 +4904,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979920</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4849,6 +5029,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979921</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4969,6 +5154,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979922</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5089,6 +5279,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979923</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5209,6 +5404,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979925</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5329,6 +5529,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979927</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5449,6 +5654,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979928</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5569,6 +5779,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979929</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5689,6 +5904,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979930</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5809,6 +6029,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979931</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5929,6 +6154,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979932</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6049,6 +6279,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979933</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6169,6 +6404,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979934</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6289,6 +6529,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979936</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6409,6 +6654,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979937</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6529,6 +6779,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979939</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6649,6 +6904,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979940</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6769,6 +7029,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979943</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6889,6 +7154,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979944</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7009,6 +7279,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979945</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7129,6 +7404,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979946</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7249,8 +7529,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130979948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>